--- a/Documentação/Custos do Projeto.xlsx
+++ b/Documentação/Custos do Projeto.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTG-2025\Desktop\Apex\Documentação\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTG-2025\Desktop\PROJETOS\Apex\Documentação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40558099-C5B3-47E9-91FD-AE216D780B3A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDCFC83-BAAB-41FF-82EC-98D6B75FFA23}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="47">
   <si>
     <t>Cargo</t>
   </si>
@@ -329,7 +329,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -370,6 +370,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -391,24 +409,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -421,6 +421,7 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -734,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" style="1" bestFit="1" customWidth="1"/>
@@ -746,24 +747,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="27"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -823,7 +824,7 @@
         <v>55</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" ref="F5:F8" si="0">C5*D5*E5</f>
+        <f t="shared" ref="F5:F7" si="0">C5*D5*E5</f>
         <v>66000</v>
       </c>
     </row>
@@ -832,7 +833,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2">
         <v>320</v>
@@ -853,7 +854,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="2">
         <v>320</v>
@@ -862,101 +863,94 @@
         <v>6</v>
       </c>
       <c r="E7" s="3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F7" s="3">
         <f t="shared" si="0"/>
-        <v>105600</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2">
-        <v>220</v>
-      </c>
-      <c r="D8" s="2">
+        <v>29</v>
+      </c>
+      <c r="B8" s="27">
+        <f>SUM(F4:F7)</f>
+        <v>334800</v>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3">
+        <v>5000</v>
+      </c>
+      <c r="C12" s="2">
         <v>6</v>
       </c>
-      <c r="E8" s="3">
-        <v>30</v>
-      </c>
-      <c r="F8" s="3">
-        <f t="shared" si="0"/>
-        <v>39600</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="21">
-        <f>SUM(F4:F8)</f>
-        <v>384000</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="23"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="7"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>21</v>
+      <c r="D12" s="3">
+        <v>30000</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="C13" s="2">
         <v>6</v>
       </c>
       <c r="D13" s="3">
-        <v>180000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="C14" s="2">
         <v>6</v>
       </c>
       <c r="D14" s="3">
-        <v>6000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" s="3">
         <v>500</v>
@@ -970,78 +964,72 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C16" s="2">
         <v>6</v>
       </c>
       <c r="D16" s="3">
-        <v>3000</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="F16" s="15"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="3">
-        <v>1000</v>
-      </c>
-      <c r="C17" s="2">
-        <v>6</v>
-      </c>
-      <c r="D17" s="3">
-        <v>6000</v>
-      </c>
-      <c r="F17" s="15"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="21">
-        <f>SUM(D13:D17)</f>
-        <v>198000</v>
-      </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="23"/>
+      <c r="B17" s="27">
+        <f>SUM(D12:D16)</f>
+        <v>48000</v>
+      </c>
+      <c r="C17" s="28"/>
+      <c r="D17" s="29"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="22"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="30"/>
+      <c r="A20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>24</v>
+      <c r="A21" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="3">
+        <v>3500</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22" s="3">
-        <v>3500</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="F22" s="8"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F23" s="8"/>
+        <v>5000</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" s="3">
         <v>5000</v>
@@ -1049,78 +1037,70 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" s="3">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="11">
-        <f>SUM(B22:B25)</f>
-        <v>15100</v>
-      </c>
+      <c r="B25" s="11">
+        <f>SUM(B21:B24)</f>
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="25"/>
+      <c r="C27" s="26"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="20"/>
+      <c r="A28" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="17"/>
+      <c r="C28" s="10">
+        <v>334800</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" s="17"/>
       <c r="C29" s="10">
-        <v>384000</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="10">
-        <v>198000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="10">
-        <v>15100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="10">
-        <f>SUM(C29:C31)</f>
-        <v>597100</v>
+        <f>SUM(C28:C30)</f>
+        <v>399300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B8:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1129,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CFBB270-1802-4457-8FAF-158E834D4990}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.5546875" bestFit="1" customWidth="1"/>
@@ -1139,12 +1119,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -1228,12 +1208,12 @@
       <c r="A8" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="27">
         <f>SUM(D4:D7)</f>
         <v>42000</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="23"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="31" t="s">
@@ -1290,20 +1270,20 @@
       <c r="A15" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="27">
         <f>SUM(C12:C14)</f>
         <v>7500</v>
       </c>
-      <c r="C15" s="23"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C15" s="29"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="32" t="s">
         <v>44</v>
       </c>
       <c r="B17" s="32"/>
       <c r="C17" s="32"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>8</v>
       </c>
@@ -1314,7 +1294,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>15</v>
       </c>
@@ -1325,7 +1305,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>18</v>
       </c>
@@ -1336,7 +1316,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>27</v>
       </c>
@@ -1347,24 +1327,24 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="27">
         <f>SUM(C19:C21)</f>
         <v>9000</v>
       </c>
-      <c r="C22" s="23"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C22" s="29"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="33" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="34"/>
       <c r="C24" s="13"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>36</v>
       </c>
@@ -1374,7 +1354,7 @@
       </c>
       <c r="E25" s="14"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>37</v>
       </c>
@@ -1382,8 +1362,10 @@
         <f>SUM(C12:C14)</f>
         <v>7500</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>38</v>
       </c>
@@ -1391,8 +1373,10 @@
         <f>SUM(C19:C21)</f>
         <v>9000</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>35</v>
       </c>
@@ -1400,6 +1384,40 @@
         <f>SUM(B25:B27)</f>
         <v>58500</v>
       </c>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+    </row>
+    <row r="33" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E33" s="35"/>
+      <c r="F33" s="35"/>
+    </row>
+    <row r="34" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+    </row>
+    <row r="35" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+    </row>
+    <row r="36" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/Documentação/Custos do Projeto.xlsx
+++ b/Documentação/Custos do Projeto.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTG-2025\Desktop\PROJETOS\Apex\Documentação\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTG-2025\Desktop\Apex\Documentação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDCFC83-BAAB-41FF-82EC-98D6B75FFA23}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0D3275-2A7E-4A61-ADDF-C314F8B1413E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -364,6 +364,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -421,7 +422,6 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -747,24 +747,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="22"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -874,22 +874,22 @@
       <c r="A8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="28">
         <f>SUM(F4:F7)</f>
         <v>334800</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="30"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
       <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -981,18 +981,18 @@
       <c r="A17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="28">
         <f>SUM(D12:D16)</f>
         <v>48000</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="30"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="22"/>
+      <c r="B19" s="23"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
@@ -1045,44 +1045,44 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="25"/>
-      <c r="C27" s="26"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="17"/>
+      <c r="B28" s="18"/>
       <c r="C28" s="10">
         <v>334800</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="17"/>
+      <c r="B29" s="18"/>
       <c r="C29" s="10">
         <v>48000</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="17"/>
+      <c r="B30" s="18"/>
       <c r="C30" s="10">
         <v>16500</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="17"/>
+      <c r="B31" s="18"/>
       <c r="C31" s="10">
         <f>SUM(C28:C30)</f>
         <v>399300</v>
@@ -1119,12 +1119,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -1208,19 +1208,19 @@
       <c r="A8" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="28">
         <f>SUM(D4:D7)</f>
         <v>42000</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="30"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
@@ -1270,18 +1270,18 @@
       <c r="A15" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="28">
         <f>SUM(C12:C14)</f>
         <v>7500</v>
       </c>
-      <c r="C15" s="29"/>
+      <c r="C15" s="30"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
@@ -1331,17 +1331,17 @@
       <c r="A22" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="28">
         <f>SUM(C19:C21)</f>
         <v>9000</v>
       </c>
-      <c r="C22" s="29"/>
+      <c r="C22" s="30"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="33" t="s">
+      <c r="A24" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="34"/>
+      <c r="B24" s="35"/>
       <c r="C24" s="13"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -1362,8 +1362,8 @@
         <f>SUM(C12:C14)</f>
         <v>7500</v>
       </c>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
@@ -1373,8 +1373,8 @@
         <f>SUM(C19:C21)</f>
         <v>9000</v>
       </c>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
@@ -1384,40 +1384,40 @@
         <f>SUM(B25:B27)</f>
         <v>58500</v>
       </c>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
     </row>
     <row r="33" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
     </row>
     <row r="34" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
     </row>
     <row r="35" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
     </row>
     <row r="36" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E36" s="35"/>
-      <c r="F36" s="35"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="7">
